--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -548,7 +548,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>22901.85</v>
+        <v>22816.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>28.64</v>
+        <v>28.53</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>799.6456005586591</v>
+        <v>799.7476340694005</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.2371450922848455</v>
+        <v>0.2372012566902866</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03491620111731843</v>
+        <v>0.03505082369435682</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>97.42901845696909</v>
+        <v>97.44025133805732</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>71.12264493103012</v>
+        <v>71.12601479535658</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>28.95523521396749</v>
+        <v>28.95601750390042</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23153.92645199027</v>
+        <v>23157.50649081651</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.01100681613014975</v>
+        <v>0.01493226441992346</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>36.9771447323891</v>
+        <v>36.98215891348526</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29568.61110647574</v>
+        <v>29576.39409383843</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.2911014222202897</v>
+        <v>0.2962551319132585</v>
       </c>
     </row>
     <row r="15"/>
@@ -4105,7 +4105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4196,6 +4196,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>22816.8</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.401515151515</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.23720125669</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -547,7 +547,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>22816.8</v>
+        <v>22787.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>28.53</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>799.7476340694005</v>
+        <v>799.5508771929825</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.2372012566902866</v>
+        <v>0.2369128252844255</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03505082369435682</v>
+        <v>0.03508771929824561</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>97.44025133805732</v>
+        <v>97.3825650568851</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>71.12601479535658</v>
+        <v>71.10870891100492</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>28.95601750390042</v>
+        <v>28.95200006646164</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23157.50649081651</v>
+        <v>23148.59704963069</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.01493226441992346</v>
+        <v>0.0158596514547944</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>36.98215891348526</v>
+        <v>36.95786325325423</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29576.39409383843</v>
+        <v>29549.69198331772</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.2962551319132585</v>
+        <v>0.2967671316931311</v>
       </c>
     </row>
     <row r="15"/>
@@ -4105,7 +4105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4229,6 +4229,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>22787.2</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.401515151515</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.236912825284</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>22787.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>28.5</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.4015151515151515</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>799.5508771929825</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.2369128252844255</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>59.84848484848485</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>97.3825650568851</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>71.10870891100492</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>28.95200006646164</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>23148.59704963069</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>0.0158596514547944</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>36.95786325325423</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>29549.69198331772</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.2967671316931311</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,17 +811,17 @@
       <c r="B18" t="n">
         <v>7</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.3344336240888997</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.2342406890298372</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.3042405004517932</v>
       </c>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n">
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,19 +834,19 @@
       <c r="B19" t="n">
         <v>8</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.2653102993441867</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.1793215921783975</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.2087496993406504</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="30" t="n">
         <v>0.1730967340143112</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,17 +859,17 @@
       <c r="B20" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.02964426021457878</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.2211416042343128</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.1736020897012249</v>
       </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n">
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -867,17 +882,17 @@
       <c r="B21" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>-0.01141617236566639</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.1661927584662644</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.158578639409193</v>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -890,21 +905,20 @@
       <c r="B22" t="n">
         <v>9</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>0.05371975100751136</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.2549536987899426</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1666948304525033</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1040,16 +1054,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>9128.700000000001</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>40.95</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1059,16 +1073,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>9714.950000000001</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>36.98</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1078,16 +1092,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>10182.05</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>34.55</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1097,16 +1111,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>10506.15</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>34.6</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1116,16 +1130,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>10726</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>28.2</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1135,16 +1149,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>11361.35</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>33.01</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1154,16 +1168,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>11390.85</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>31.61</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1173,16 +1187,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>11223.55</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>29.5</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1192,16 +1206,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>11543.55</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>30.54</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1211,16 +1225,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>11413.65</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>30.24</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1230,16 +1244,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>10621</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>26.83</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1249,16 +1263,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>11131.1</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>27.14</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1268,16 +1282,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>11201.95</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>27.11</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1287,16 +1301,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>10616.3</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>23.74</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1306,16 +1320,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>10042.8</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>22.75</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1325,16 +1339,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>11194.7</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>24.69</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1344,16 +1358,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>11867</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1363,16 +1377,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>11654.45</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>24.69</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1382,16 +1396,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>11868.15</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>24.45</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1401,16 +1415,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>12093.5</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>26.31</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1420,16 +1434,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>11885.75</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>26.12</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1439,16 +1453,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>11596.65</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>25.21</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1458,16 +1472,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>11411.25</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>23.88</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1477,16 +1491,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>11352.25</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>23.47</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1496,16 +1510,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>11943.55</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>24.71</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1515,16 +1529,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>12623.35</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>24.98</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1534,16 +1548,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>13401.45</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>26.49</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1553,16 +1567,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>14140</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>27.41</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1572,16 +1586,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>14693.85</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>25.32</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1591,16 +1605,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>15141.05</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>26.77</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1610,16 +1624,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>14566.3</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>25.08</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1629,16 +1643,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>15963.25</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>24.85</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1648,16 +1662,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>17077.05</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>26.51</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1667,16 +1681,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>17884.7</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>27.5</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1686,16 +1700,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>17831.1</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>26.96</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1705,16 +1719,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>17766</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>33.63</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1724,16 +1738,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>18893</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>35.49</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1743,16 +1757,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>19308.75</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>39.46</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1762,16 +1776,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>20831.95</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>42.33</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1781,16 +1795,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>21860.95</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>45.37</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1800,16 +1814,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>21925.45</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>44.22</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1819,16 +1833,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>22311.95</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>45.66</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1838,16 +1852,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>20876.7</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>42.98</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1857,16 +1871,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>20906.65</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>41.98</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1876,16 +1890,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>21141.2</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>43.3</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1895,16 +1909,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>19850.95</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>38.76</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1914,16 +1928,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>17750.55</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>33.44</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1933,16 +1947,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>19120.35</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>33.71</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1952,16 +1966,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>19873.15</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>34.01</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1971,16 +1985,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>21125.55</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>34.26</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1990,16 +2004,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>21988.65</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>35.27</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2009,16 +2023,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>21361.3</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>33.8</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2028,16 +2042,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>20750.3</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>32.1</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2047,16 +2061,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>21038.7</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>32.84</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2066,16 +2080,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>22045.95</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>34.12</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2085,16 +2099,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>22395.4</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>33.41</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2104,16 +2118,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>22276.9</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>33.56</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2123,16 +2137,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>21490.9</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>31.81</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2142,16 +2156,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>21847.35</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>32.56</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2161,16 +2175,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>19430.9</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>30.61</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2180,16 +2194,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>22000.05</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>33.45</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2199,16 +2213,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>22571.4</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>28.92</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2218,16 +2232,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>22774.25</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>29.17</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2237,16 +2251,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>23138.45</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>30.41</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2256,16 +2270,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>23536.8</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>29.44</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2367,13 +2381,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>42551</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>4614.3</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>35.71</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2381,12 +2395,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$42,D2,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$42,D2,$C$2:$C$42,C2)+1)/2)/COUNTIFS($D$2:$D$42,D2,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2394,31 +2408,31 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="30">
         <f>IFERROR((B42/B2)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>42643</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>5103</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>37.34</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2426,12 +2440,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$42,D3,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$42,D3,$C$2:$C$42,C3)+1)/2)/COUNTIFS($D$2:$D$42,D3,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2439,28 +2453,28 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16" t="n"/>
+      <c r="L3" s="30" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>42735</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>4738.85</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>31.81</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2468,12 +2482,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$42,D4,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$42,D4,$C$2:$C$42,C4)+1)/2)/COUNTIFS($D$2:$D$42,D4,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2481,28 +2495,28 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16" t="n"/>
+      <c r="L4" s="30" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>42825</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>5699.36</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>40.13</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2510,12 +2524,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$42,D5,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$42,D5,$C$2:$C$42,C5)+1)/2)/COUNTIFS($D$2:$D$42,D5,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2523,28 +2537,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>42916</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>5964.59</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>39.86</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2552,15 +2566,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$42,D6,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$42,D6,$C$2:$C$42,C6)+1)/2)/COUNTIFS($D$2:$D$42,D6,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2568,28 +2582,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>43008</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>6227.38</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>48.37</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2597,15 +2611,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$42,D7,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$42,D7,$C$2:$C$42,C7)+1)/2)/COUNTIFS($D$2:$D$42,D7,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2613,28 +2627,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>7314.16</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>55.74</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2642,15 +2656,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$42,D8,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$42,D8,$C$2:$C$42,C8)+1)/2)/COUNTIFS($D$2:$D$42,D8,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2658,28 +2672,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>6598.51</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>51.68</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2687,15 +2701,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$42,D9,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$42,D9,$C$2:$C$42,C9)+1)/2)/COUNTIFS($D$2:$D$42,D9,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2703,28 +2717,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>6419.84</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>44.99</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2732,15 +2746,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$42,D10,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$42,D10,$C$2:$C$42,C10)+1)/2)/COUNTIFS($D$2:$D$42,D10,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2748,28 +2762,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>6118.61</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>43.35</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2777,15 +2791,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$42,D11,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$42,D11,$C$2:$C$42,C11)+1)/2)/COUNTIFS($D$2:$D$42,D11,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2793,28 +2807,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>6339.3</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>40.02</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2822,15 +2836,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$42,D12,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$42,D12,$C$2:$C$42,C12)+1)/2)/COUNTIFS($D$2:$D$42,D12,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2838,28 +2852,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>6503.95</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>34.86</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2867,15 +2881,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$42,D13,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$42,D13,$C$2:$C$42,C13)+1)/2)/COUNTIFS($D$2:$D$42,D13,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2883,28 +2897,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>6346.55</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>32.84</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2912,15 +2926,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$42,D14,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$42,D14,$C$2:$C$42,C14)+1)/2)/COUNTIFS($D$2:$D$42,D14,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2928,28 +2942,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>5912.2</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>26.65</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2957,15 +2971,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$42,D15,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$42,D15,$C$2:$C$42,C15)+1)/2)/COUNTIFS($D$2:$D$42,D15,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2973,28 +2987,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>6321.6</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>27.13</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3002,15 +3016,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$42,D16,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$42,D16,$C$2:$C$42,C16)+1)/2)/COUNTIFS($D$2:$D$42,D16,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3018,28 +3032,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>4493.25</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>19.67</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3047,15 +3061,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$42,D17,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$42,D17,$C$2:$C$42,C17)+1)/2)/COUNTIFS($D$2:$D$42,D17,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3063,28 +3077,28 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="30">
         <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="16" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>5626.2</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>66.98</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3092,15 +3106,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$42,D18,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$42,D18,$C$2:$C$42,C18)+1)/2)/COUNTIFS($D$2:$D$42,D18,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3108,42 +3122,42 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="30">
         <f>IFERROR((B38/B18)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L18" s="16" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>6481.45</v>
       </c>
-      <c r="C19" s="7" t="n"/>
+      <c r="C19" s="25" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$42,D19,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$42,D19,$C$2:$C$42,C19)+1)/2)/COUNTIFS($D$2:$D$42,D19,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3151,28 +3165,28 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="30">
         <f>IFERROR((B39/B19)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L19" s="16" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>7862.9</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>145.06</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3180,15 +3194,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$42,D20,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$42,D20,$C$2:$C$42,C20)+1)/2)/COUNTIFS($D$2:$D$42,D20,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3196,28 +3210,28 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="30">
         <f>IFERROR((B40/B20)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L20" s="16" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>8988.9</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>40.58</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3225,15 +3239,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$42,D21,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$42,D21,$C$2:$C$42,C21)+1)/2)/COUNTIFS($D$2:$D$42,D21,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3241,28 +3255,28 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="30">
         <f>IFERROR((B41/B21)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L21" s="16" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>10182.05</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>34.55</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3270,15 +3284,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$42,D22,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$42,D22,$C$2:$C$42,C22)+1)/2)/COUNTIFS($D$2:$D$42,D22,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3286,28 +3300,28 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="30">
         <f>IFERROR((B42/B22)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L22" s="16" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>11361.35</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>33.01</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3315,15 +3329,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$42,D23,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$42,D23,$C$2:$C$42,C23)+1)/2)/COUNTIFS($D$2:$D$42,D23,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3331,25 +3345,25 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="16" t="n"/>
+      <c r="K23" s="30" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>11543.55</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>30.54</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3357,15 +3371,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$42,D24,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$42,D24,$C$2:$C$42,C24)+1)/2)/COUNTIFS($D$2:$D$42,D24,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3373,25 +3387,25 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="16" t="n"/>
+      <c r="K24" s="30" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>11131.1</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>27.14</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3399,15 +3413,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$42,D25,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$42,D25,$C$2:$C$42,C25)+1)/2)/COUNTIFS($D$2:$D$42,D25,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3415,25 +3429,25 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="30">
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>10042.8</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>22.75</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3441,15 +3455,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$42,D26,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$42,D26,$C$2:$C$42,C26)+1)/2)/COUNTIFS($D$2:$D$42,D26,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3457,25 +3471,25 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="30">
         <f>IFERROR((B38/B26)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>11654.45</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>24.69</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3483,15 +3497,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$42,D27,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$42,D27,$C$2:$C$42,C27)+1)/2)/COUNTIFS($D$2:$D$42,D27,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3499,25 +3513,25 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="30">
         <f>IFERROR((B39/B27)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>11885.75</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>26.12</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3525,15 +3539,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$42,D28,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$42,D28,$C$2:$C$42,C28)+1)/2)/COUNTIFS($D$2:$D$42,D28,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3541,25 +3555,25 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="30">
         <f>IFERROR((B40/B28)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>11352.25</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>23.47</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3567,15 +3581,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$42,D29,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$42,D29,$C$2:$C$42,C29)+1)/2)/COUNTIFS($D$2:$D$42,D29,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3583,25 +3597,25 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="30">
         <f>IFERROR((B41/B29)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>13401.45</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>26.49</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3609,15 +3623,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$42,D30,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$42,D30,$C$2:$C$42,C30)+1)/2)/COUNTIFS($D$2:$D$42,D30,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3625,25 +3639,25 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="30">
         <f>IFERROR((B42/B30)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>15141.05</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>26.77</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3651,15 +3665,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$42,D31,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$42,D31,$C$2:$C$42,C31)+1)/2)/COUNTIFS($D$2:$D$42,D31,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3667,22 +3681,22 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="J31" s="30" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>17077.05</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>26.51</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3690,15 +3704,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$42,D32,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$42,D32,$C$2:$C$42,C32)+1)/2)/COUNTIFS($D$2:$D$42,D32,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3706,22 +3720,22 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="J32" s="30" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>17766</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>33.63</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3729,15 +3743,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$42,D33,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$42,D33,$C$2:$C$42,C33)+1)/2)/COUNTIFS($D$2:$D$42,D33,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3745,22 +3759,22 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="30">
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>20831.95</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>42.33</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3768,15 +3782,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$42,D34,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$42,D34,$C$2:$C$42,C34)+1)/2)/COUNTIFS($D$2:$D$42,D34,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3784,22 +3798,22 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="30">
         <f>IFERROR(B38/B34-1,"")</f>
         <v/>
       </c>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>22311.95</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>45.66</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3807,15 +3821,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$42,D35,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$42,D35,$C$2:$C$42,C35)+1)/2)/COUNTIFS($D$2:$D$42,D35,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3823,22 +3837,22 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="30">
         <f>IFERROR(B39/B35-1,"")</f>
         <v/>
       </c>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>21141.2</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>43.3</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3846,15 +3860,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$42,D36,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$42,D36,$C$2:$C$42,C36)+1)/2)/COUNTIFS($D$2:$D$42,D36,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3862,22 +3876,22 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="30">
         <f>IFERROR(B40/B36-1,"")</f>
         <v/>
       </c>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>19120.35</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>33.71</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3885,15 +3899,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="33">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="30">
         <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="30">
         <f>IF(C37="","",(COUNTIFS($D$2:$D$42,D37,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$42,D37,$C$2:$C$42,C37)+1)/2)/COUNTIFS($D$2:$D$42,D37,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3901,22 +3915,22 @@
         <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="30">
         <f>IFERROR(B41/B37-1,"")</f>
         <v/>
       </c>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>21988.65</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>35.27</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3924,15 +3938,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="33">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="30">
         <f>IF(AND(D38=D34,E34&lt;&gt;""),E38/E34-1,"")</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="30">
         <f>IF(C38="","",(COUNTIFS($D$2:$D$42,D38,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$42,D38,$C$2:$C$42,C38)+1)/2)/COUNTIFS($D$2:$D$42,D38,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3940,22 +3954,22 @@
         <f>IF(G38="","",IF(G38&lt;=20%,"Q1 Cheapest",IF(G38&lt;=40%,"Q2",IF(G38&lt;=60%,"Q3",IF(G38&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="30">
         <f>IFERROR(B42/B38-1,"")</f>
         <v/>
       </c>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="16" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="30" t="n"/>
+      <c r="L38" s="30" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>21038.7</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>32.84</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3963,15 +3977,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="33">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="30">
         <f>IF(AND(D39=D35,E35&lt;&gt;""),E39/E35-1,"")</f>
         <v/>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="30">
         <f>IF(C39="","",(COUNTIFS($D$2:$D$42,D39,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$42,D39,$C$2:$C$42,C39)+1)/2)/COUNTIFS($D$2:$D$42,D39,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3979,19 +3993,19 @@
         <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I39" s="16" t="n"/>
-      <c r="J39" s="16" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="16" t="n"/>
+      <c r="I39" s="30" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="30" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>22276.9</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>33.56</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3999,15 +4013,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="33">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="30">
         <f>IF(AND(D40=D36,E36&lt;&gt;""),E40/E36-1,"")</f>
         <v/>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="30">
         <f>IF(C40="","",(COUNTIFS($D$2:$D$42,D40,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$42,D40,$C$2:$C$42,C40)+1)/2)/COUNTIFS($D$2:$D$42,D40,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -4015,19 +4029,19 @@
         <f>IF(G40="","",IF(G40&lt;=20%,"Q1 Cheapest",IF(G40&lt;=40%,"Q2",IF(G40&lt;=60%,"Q3",IF(G40&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I40" s="16" t="n"/>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="16" t="n"/>
+      <c r="I40" s="30" t="n"/>
+      <c r="J40" s="30" t="n"/>
+      <c r="K40" s="30" t="n"/>
+      <c r="L40" s="30" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>19430.9</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>30.61</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4035,15 +4049,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="33">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="30">
         <f>IF(AND(D41=D37,E37&lt;&gt;""),E41/E37-1,"")</f>
         <v/>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="30">
         <f>IF(C41="","",(COUNTIFS($D$2:$D$42,D41,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$42,D41,$C$2:$C$42,C41)+1)/2)/COUNTIFS($D$2:$D$42,D41,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -4051,19 +4065,19 @@
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="16" t="n"/>
+      <c r="I41" s="30" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="30" t="n"/>
+      <c r="L41" s="30" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>22774.25</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>29.17</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4071,15 +4085,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="33">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="30">
         <f>IF(AND(D42=D38,E38&lt;&gt;""),E42/E38-1,"")</f>
         <v/>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="30">
         <f>IF(C42="","",(COUNTIFS($D$2:$D$42,D42,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$42,D42,$C$2:$C$42,C42)+1)/2)/COUNTIFS($D$2:$D$42,D42,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -4087,10 +4101,10 @@
         <f>IF(G42="","",IF(G42&lt;=20%,"Q1 Cheapest",IF(G42&lt;=40%,"Q2",IF(G42&lt;=60%,"Q3",IF(G42&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="16" t="n"/>
+      <c r="I42" s="30" t="n"/>
+      <c r="J42" s="30" t="n"/>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4167,30 +4181,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>22901.85</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>28.64</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.401515151515</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.237145092285</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -4200,30 +4214,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>22816.8</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>28.53</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.401515151515</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.23720125669</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -4233,30 +4247,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>22787.2</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>28.5</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.401515151515</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.236912825284</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4376,4 +4390,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty Midcap 150 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,6 +153,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4289,6 +4292,3112 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E155"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY Midcap 150 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Retrieved 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Index Constituent CSV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3M India Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3MINDIA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Diversified</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Abbott India Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ACC Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Adani Total Gas Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aditya Birla Capital Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AIA Engineering Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AIAENG</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ajanta Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AJANTPHARM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alkem Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Anthem Biosciences Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Apar Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>APARINDS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>APL Apollo Tubes Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Apollo Tyres Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ashok Leyland Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Astral Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AU Small Finance Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Authum Investment &amp; Infrastructure Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AIIL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AWL Agri Business Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AWL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bajaj Housing Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BAJAJHFL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Balkrishna Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BALKRISIND</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bank of India</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bank of Maharashtra</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Berger Paints India Ltd.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BERGEPAINT</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bharat Dynamics Ltd.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BDL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bharat Forge Ltd.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bharat Heavy Electricals Ltd.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bharti Hexacom Ltd.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BHARTIHEXA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Billionbrains Garage Ventures Ltd.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GROWW</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Biocon Ltd.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Blue Star Ltd.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BLUESTARCO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BSE Ltd.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cochin Shipyard Ltd.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>COCHINSHIP</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Coforge Ltd.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Colgate Palmolive (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Container Corporation of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Coromandel International Ltd.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>COROMANDEL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CRISIL Ltd.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Dabur India Ltd.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Dalmia Bharat Ltd.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Dixon Technologies (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Endurance Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ENDURANCE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Escorts Kubota Ltd.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ESCORTS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Exide Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Federal Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Fortis Healthcare Ltd.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FSN E-Commerce Ventures Ltd.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GE Vernova T&amp;D India Ltd.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>General Insurance Corporation of India</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GICRE</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>GLAXO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Global Health Ltd.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MEDANTA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GMR Airports Ltd.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Godfrey Phillips India Ltd.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GODFRYPHLP</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Godrej Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GODREJIND</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Diversified</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Godrej Properties Ltd.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>56</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Gujarat Fluorochemicals Ltd.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FLUOROCHEM</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>57</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Havells India Ltd.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>HDB Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>HDBFS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Hero MotoCorp Ltd.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Hexaware Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HEXT</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>61</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Hindustan Petroleum Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Hitachi Energy India Ltd.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>63</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Honeywell Automation India Ltd.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HONAUT</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>64</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Housing &amp; Urban Development Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HUDCO</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>65</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>66</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Asset Management Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ICICIAMC</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>67</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Life Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>68</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>IDFC First Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>69</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Indian Bank</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>70</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>71</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Indian Renewable Energy Development Agency Ltd.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>IREDA</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>72</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Indus Towers Ltd.</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>73</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>IndusInd Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>74</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Info Edge (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>75</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>76</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ITC Hotels Ltd.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ITCHOTELS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>77</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>J.K. Cement Ltd.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>JKCEMENT</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>78</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Jindal Stainless Ltd.</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>JSL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>79</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>JSW Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>80</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>JSW Infrastructure Ltd.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>JSWINFRA</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>81</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Jubilant Foodworks Ltd.</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>82</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>K.P.R. Mill Ltd.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>KPRMILL</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Textiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>83</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Kalyan Jewellers India Ltd.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>84</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>KEI Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>85</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>KPIT Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>86</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>L&amp;T Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>87</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>L&amp;T Technology Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>LTTS</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>88</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Laurus Labs Ltd.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>89</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Lenskart Solutions Ltd.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>90</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>LG Electronics India Ltd.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>LGEINDIA</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>91</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>LIC Housing Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>92</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Life Insurance Corporation of India</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>93</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Linde India Ltd.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>LINDEINDIA</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>94</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Lloyds Metals And Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>LLOYDSME</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>95</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Lupin Ltd.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>96</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>M&amp;MFIN</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>97</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Mankind Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>98</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Marico Ltd.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>99</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Max Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>100</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Motilal Oswal Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>101</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>MphasiS Ltd.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>102</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>MRF Ltd.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>MRF</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>103</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Multi Commodity Exchange of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>104</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>National Aluminium Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>105</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NHPC Ltd.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>106</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Nippon Life India Asset Management Ltd.</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>107</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NLC India Ltd.</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>108</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NMDC Ltd.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>109</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NTPC Green Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>NTPCGREEN</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>110</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Oberoi Realty Ltd.</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>111</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Oil India Ltd.</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>112</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>One 97 Communications Ltd.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>113</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ONE WAM Ltd.</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>114</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Oracle Financial Services Software Ltd.</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>115</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Page Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Textiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>116</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Patanjali Foods Ltd.</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>117</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PB Fintech Ltd.</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>118</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Persistent Systems Ltd.</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>119</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Petronet LNG Ltd.</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>120</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Phoenix Mills Ltd.</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>121</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PI Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>122</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Polycab India Ltd.</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>123</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Premier Energies Ltd.</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>PREMIERENE</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>124</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Prestige Estates Projects Ltd.</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>125</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Radico Khaitan Ltd</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>126</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Rail Vikas Nigam Ltd.</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>RVNL</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>127</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SBI Cards and Payment Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Schaeffler India Ltd.</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>129</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SJVN Ltd.</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>130</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SRF Ltd.</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>SRF</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>131</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Steel Authority of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>132</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Sundaram Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SUNDARMFIN</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>133</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Supreme Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>134</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Suzlon Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>135</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Swiggy Ltd.</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>SWIGGY</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>136</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Tata Communications Ltd.</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>137</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Tata Elxsi Ltd.</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>TATAELXSI</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>138</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Tata Investment Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>TATAINVEST</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>139</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>The New India Assurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>NIACL</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>140</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Thermax Ltd.</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>141</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Torrent Power Ltd.</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>142</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Tube Investments of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>143</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>United Breweries Ltd.</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>UBL</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>144</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>UNO Minda Ltd.</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>145</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>UPL Ltd.</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>146</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Vishal Mega Mart Ltd.</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>VMM</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>147</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Vodafone Idea Ltd.</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>148</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Voltas Ltd.</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>149</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Waaree Energies Ltd.</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>WAAREEENER</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>150</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Yes Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>YESBANK</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
@@ -4390,43 +7499,4 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Nifty Midcap 150 Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Official composition data is not currently available for this index.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22787.2</v>
+        <v>22928.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.5</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>799.5508771929825</v>
+        <v>799.7506103941402</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2369128252844255</v>
+        <v>0.2371796018688368</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03508771929824561</v>
+        <v>0.03487966515521451</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>97.3825650568851</v>
+        <v>97.43592037376736</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.10870891100492</v>
+        <v>71.12471550606961</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.95200006646164</v>
+        <v>28.95571588317308</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23148.59704963069</v>
+        <v>23157.35145196697</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.0158596514547944</v>
+        <v>0.009965674334603492</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>36.95786325325423</v>
+        <v>36.98001137390664</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29549.69198331772</v>
+        <v>29574.78666866408</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2967671316931311</v>
+        <v>0.2898504141578877</v>
       </c>
     </row>
     <row r="16">
@@ -4122,7 +4122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4279,6 +4279,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>22928.85</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.401515151515</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.237179601869</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22928.85</v>
+        <v>22469.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.67</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.4015151515151515</v>
+        <v>0.3863636363636364</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>799.7506103941402</v>
+        <v>799.6405693950178</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2371796018688368</v>
+        <v>0.2371694443873327</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03487966515521451</v>
+        <v>0.03558718861209964</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>59.84848484848485</v>
+        <v>61.36363636363637</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>97.43592037376736</v>
+        <v>97.43388887746653</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.12471550606961</v>
+        <v>72.18471211778541</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.95571588317308</v>
+        <v>28.95557440396642</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23157.35145196697</v>
+        <v>23154.05200354751</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.009965674334603492</v>
+        <v>0.03044748768563754</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>36.98001137390664</v>
+        <v>36.9791663047827</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29574.78666866408</v>
+        <v>29570.0415997095</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2898504141578877</v>
+        <v>0.3159845660065017</v>
       </c>
     </row>
     <row r="16">
@@ -4122,7 +4122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4312,6 +4312,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>22469.9</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.386363636364</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.237169444387</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4352,7 +4385,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22469.9</v>
+        <v>22437</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.1</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>799.6405693950178</v>
+        <v>799.6079828937991</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2371694443873327</v>
+        <v>0.2370989909092849</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03558718861209964</v>
+        <v>0.03563791874554526</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>97.43388887746653</v>
+        <v>97.41979818185698</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>72.18471211778541</v>
+        <v>72.18048490910255</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.95557440396642</v>
+        <v>28.95459308766504</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23154.05200354751</v>
+        <v>23152.32377433858</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03044748768563754</v>
+        <v>0.03188143576853331</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>36.9791663047827</v>
+        <v>36.9733176596265</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29570.0415997095</v>
+        <v>29564.15995470562</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3159845660065017</v>
+        <v>0.3176520905070028</v>
       </c>
     </row>
     <row r="16">
@@ -4122,7 +4122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4345,6 +4345,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>22437</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.386363636364</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.237098990909</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4385,7 +4418,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22437</v>
+        <v>22071.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.06</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>799.6079828937991</v>
+        <v>799.6847826086956</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2370989909092849</v>
+        <v>0.2372226084260869</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03563791874554526</v>
+        <v>0.03623188405797102</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>97.41979818185698</v>
+        <v>97.44452168521738</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>72.18048490910255</v>
+        <v>72.18790196011066</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.95459308766504</v>
+        <v>28.95631490307764</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23152.32377433858</v>
+        <v>23155.92438841658</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03188143576853331</v>
+        <v>0.04914184431440738</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>36.9733176596265</v>
+        <v>36.98427639562707</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29564.15995470562</v>
+        <v>29575.76302937695</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3176520905070028</v>
+        <v>0.3400100143343141</v>
       </c>
     </row>
     <row r="16">
@@ -4122,7 +4122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4378,6 +4378,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>22071.3</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.386363636364</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.237222608426</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4418,7 +4451,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22071.3</v>
+        <v>21853.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.6</v>
+        <v>27.33</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3863636363636364</v>
+        <v>0.3560606060606061</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>799.6847826086956</v>
+        <v>799.6084888401025</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2372226084260869</v>
+        <v>0.2370726953891595</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03623188405797102</v>
+        <v>0.03658982802780827</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>61.36363636363637</v>
+        <v>64.39393939393939</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>97.44452168521738</v>
+        <v>97.4145390778319</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>72.18790196011066</v>
+        <v>74.30011929910714</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.95631490307764</v>
+        <v>28.95422682863472</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23155.92438841658</v>
+        <v>23152.04555997816</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04914184431440738</v>
+        <v>0.05943018033789693</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>36.98427639562707</v>
+        <v>36.97113475580579</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29575.76302937695</v>
+        <v>29562.43319279366</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3400100143343141</v>
+        <v>0.3527674627078594</v>
       </c>
     </row>
     <row r="16">
@@ -4122,7 +4122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4411,6 +4411,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>21853.3</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.356060606061</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.237072695389</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4451,7 +4484,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4521,17 +4554,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3M India Ltd.</t>
+          <t>Abbott India Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4541,17 +4574,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Abbott India Ltd.</t>
+          <t>Adani Total Gas Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -4561,17 +4594,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ACC Ltd.</t>
+          <t>Aditya Birla Capital Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4581,17 +4614,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Adani Total Gas Ltd.</t>
+          <t>AIA Engineering Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>AIAENG</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4601,17 +4634,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aditya Birla Capital Ltd.</t>
+          <t>Ajanta Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4621,17 +4654,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AIA Engineering Ltd.</t>
+          <t>Alkem Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4641,12 +4674,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ajanta Pharmaceuticals Ltd.</t>
+          <t>Anthem Biosciences Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>ANTHEM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4661,17 +4694,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>Apar Industries Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4681,17 +4714,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Anthem Biosciences Ltd.</t>
+          <t>APL Apollo Tubes Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ANTHEM</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4701,12 +4734,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Apar Industries Ltd.</t>
+          <t>Ashok Leyland Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4721,17 +4754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>APL Apollo Tubes Ltd.</t>
+          <t>Aster DM Quality Care Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ASTERDM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4741,17 +4774,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Apollo Tyres Ltd.</t>
+          <t>Astral Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4761,17 +4794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ashok Leyland Ltd.</t>
+          <t>AU Small Finance Bank Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4781,17 +4814,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Astral Ltd.</t>
+          <t>Aurobindo Pharma Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4801,12 +4834,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Ltd.</t>
+          <t>Authum Investment &amp; Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>AIIL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4821,17 +4854,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Ltd.</t>
+          <t>Bajaj Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>BAJAJHFL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4841,17 +4874,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Authum Investment &amp; Infrastructure Ltd.</t>
+          <t>Balkrishna Industries Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AIIL</t>
+          <t>BALKRISIND</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4861,17 +4894,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AWL Agri Business Ltd.</t>
+          <t>Bank of India</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4881,12 +4914,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bajaj Housing Finance Ltd.</t>
+          <t>Bank of Maharashtra</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BAJAJHFL</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4901,17 +4934,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Balkrishna Industries Ltd.</t>
+          <t>Berger Paints India Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BALKRISIND</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -4921,17 +4954,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bank of India</t>
+          <t>Bharat Dynamics Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4941,17 +4974,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bank of Maharashtra</t>
+          <t>Bharat Forge Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4961,17 +4994,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Berger Paints India Ltd.</t>
+          <t>Bharat Heavy Electricals Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4981,17 +5014,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bharat Dynamics Ltd.</t>
+          <t>Bharti Hexacom Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>BHARTIHEXA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -5001,17 +5034,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bharat Forge Ltd.</t>
+          <t>Billionbrains Garage Ventures Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>GROWW</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5021,17 +5054,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Ltd.</t>
+          <t>Biocon Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5041,17 +5074,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bharti Hexacom Ltd.</t>
+          <t>Blue Star Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BHARTIHEXA</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5061,17 +5094,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Billionbrains Garage Ventures Ltd.</t>
+          <t>Cochin Shipyard Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GROWW</t>
+          <t>COCHINSHIP</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5081,17 +5114,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Biocon Ltd.</t>
+          <t>Coforge Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5101,17 +5134,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Blue Star Ltd.</t>
+          <t>Colgate Palmolive (India) Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5121,17 +5154,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BSE Ltd.</t>
+          <t>Container Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -5141,17 +5174,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cochin Shipyard Ltd.</t>
+          <t>Coromandel International Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>COCHINSHIP</t>
+          <t>COROMANDEL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5161,17 +5194,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Coforge Ltd.</t>
+          <t>CRISIL Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5214,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Colgate Palmolive (India) Ltd.</t>
+          <t>Dabur India Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5201,17 +5234,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Container Corporation of India Ltd.</t>
+          <t>Dalmia Bharat Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -5221,17 +5254,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Coromandel International Ltd.</t>
+          <t>Dixon Technologies (India) Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5241,17 +5274,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CRISIL Ltd.</t>
+          <t>EMBASSY OFFICE PARKS REIT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>EMBASSY</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -5261,17 +5294,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dabur India Ltd.</t>
+          <t>Endurance Technologies Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>ENDURANCE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5281,17 +5314,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dalmia Bharat Ltd.</t>
+          <t>Escorts Kubota Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5301,17 +5334,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dixon Technologies (India) Ltd.</t>
+          <t>Exide Industries Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5321,17 +5354,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Endurance Technologies Ltd.</t>
+          <t>Federal Bank Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5341,17 +5374,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Escorts Kubota Ltd.</t>
+          <t>Fertilisers and Chemicals Travancore Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>FACT</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5361,17 +5394,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Exide Industries Ltd.</t>
+          <t>Fortis Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5381,17 +5414,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Federal Bank Ltd.</t>
+          <t>FSN E-Commerce Ventures Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5401,17 +5434,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fortis Healthcare Ltd.</t>
+          <t>GE Vernova T&amp;D India Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5421,17 +5454,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Ltd.</t>
+          <t>General Insurance Corporation of India</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>GICRE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5441,17 +5474,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GE Vernova T&amp;D India Ltd.</t>
+          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5461,17 +5494,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>General Insurance Corporation of India</t>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GICRE</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5481,12 +5514,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
+          <t>Global Health Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5501,17 +5534,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Glenmark Pharmaceuticals Ltd.</t>
+          <t>GMR Airports Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -5521,17 +5554,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Global Health Ltd.</t>
+          <t>Godfrey Phillips India Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>GODFRYPHLP</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5541,17 +5574,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GMR Airports Ltd.</t>
+          <t>Godrej Industries Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>GODREJIND</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Diversified</t>
         </is>
       </c>
     </row>
@@ -5561,17 +5594,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Godfrey Phillips India Ltd.</t>
+          <t>Godrej Properties Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GODFRYPHLP</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -5581,17 +5614,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Godrej Industries Ltd.</t>
+          <t>Gujarat Fluorochemicals Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GODREJIND</t>
+          <t>FLUOROCHEM</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5601,17 +5634,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Godrej Properties Ltd.</t>
+          <t>Havells India Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5621,17 +5654,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gujarat Fluorochemicals Ltd.</t>
+          <t>HDB Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FLUOROCHEM</t>
+          <t>HDBFS</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5641,17 +5674,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Havells India Ltd.</t>
+          <t>Hero MotoCorp Ltd.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5661,17 +5694,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HDB Financial Services Ltd.</t>
+          <t>Hexaware Technologies Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HDBFS</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5681,17 +5714,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hero MotoCorp Ltd.</t>
+          <t>Hindustan Copper Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -5701,17 +5734,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hexaware Technologies Ltd.</t>
+          <t>Hindustan Petroleum Corporation Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -5721,17 +5754,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hindustan Petroleum Corporation Ltd.</t>
+          <t>Housing &amp; Urban Development Corporation Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>HUDCO</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5741,17 +5774,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hitachi Energy India Ltd.</t>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5761,17 +5794,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Honeywell Automation India Ltd.</t>
+          <t>ICICI Prudential Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HONAUT</t>
+          <t>ICICIAMC</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5781,12 +5814,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Housing &amp; Urban Development Corporation Ltd.</t>
+          <t>ICICI Prudential Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HUDCO</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5801,12 +5834,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ICICI Lombard General Insurance Company Ltd.</t>
+          <t>IDFC First Bank Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5821,12 +5854,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ICICI Prudential Asset Management Company Ltd.</t>
+          <t>Indian Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ICICIAMC</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5841,17 +5874,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ICICI Prudential Life Insurance Company Ltd.</t>
+          <t>Indian Hotels Co. Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5861,12 +5894,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IDFC First Bank Ltd.</t>
+          <t>Indian Overseas Bank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5881,17 +5914,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Indian Bank</t>
+          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5901,17 +5934,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
+          <t>Indian Renewable Energy Development Agency Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>IREDA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5921,17 +5954,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Indian Renewable Energy Development Agency Ltd.</t>
+          <t>Indus Towers Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -5941,17 +5974,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Indus Towers Ltd.</t>
+          <t>IndusInd Bank Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5961,17 +5994,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IndusInd Bank Ltd.</t>
+          <t>Info Edge (India) Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5981,17 +6014,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Info Edge (India) Ltd.</t>
+          <t>Ipca Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -6001,17 +6034,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ipca Laboratories Ltd.</t>
+          <t>ITC Hotels Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -6021,17 +6054,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ITC Hotels Ltd.</t>
+          <t>J.K. Cement Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>JKCEMENT</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -6041,17 +6074,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>J.K. Cement Ltd.</t>
+          <t>Jindal Stainless Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>JKCEMENT</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -6061,17 +6094,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jindal Stainless Ltd.</t>
+          <t>JSW Energy Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -6081,17 +6114,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JSW Energy Ltd.</t>
+          <t>JSW Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>JSWINFRA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -6101,17 +6134,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JSW Infrastructure Ltd.</t>
+          <t>Jubilant Foodworks Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JSWINFRA</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -6121,17 +6154,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Jubilant Foodworks Ltd.</t>
+          <t>K.P.R. Mill Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -6141,17 +6174,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>K.P.R. Mill Ltd.</t>
+          <t>Kalyan Jewellers India Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -6161,17 +6194,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Kalyan Jewellers India Ltd.</t>
+          <t>KEI Industries Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6181,17 +6214,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KEI Industries Ltd.</t>
+          <t>L&amp;T Finance Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6234,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KPIT Technologies Ltd.</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6221,17 +6254,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>L&amp;T Finance Ltd.</t>
+          <t>Laurus Labs Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -6241,17 +6274,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Lenskart Solutions Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -6261,17 +6294,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Laurus Labs Ltd.</t>
+          <t>LG Electronics India Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>LGEINDIA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -6281,17 +6314,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lenskart Solutions Ltd.</t>
+          <t>LIC Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6301,17 +6334,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LG Electronics India Ltd.</t>
+          <t>Life Insurance Corporation of India</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LGEINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6321,17 +6354,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LIC Housing Finance Ltd.</t>
+          <t>Linde India Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>LINDEINDIA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -6341,17 +6374,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Life Insurance Corporation of India</t>
+          <t>Lloyds Metals And Energy Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>LLOYDSME</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -6361,17 +6394,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Linde India Ltd.</t>
+          <t>Lodha Developers Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LINDEINDIA</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -6381,17 +6414,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lloyds Metals And Energy Ltd.</t>
+          <t>Lupin Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LLOYDSME</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -6401,17 +6434,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lupin Ltd.</t>
+          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>M&amp;MFIN</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6421,17 +6454,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
+          <t>Mankind Pharma Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>M&amp;MFIN</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -6441,17 +6474,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Mankind Pharma Ltd.</t>
+          <t>Marico Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -6461,17 +6494,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Marico Ltd.</t>
+          <t>Max Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6481,17 +6514,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Max Financial Services Ltd.</t>
+          <t>Meesho Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -6581,17 +6614,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>National Aluminium Co. Ltd.</t>
+          <t>Narayana Hrudayalaya Ltd.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -6601,17 +6634,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NHPC Ltd.</t>
+          <t>National Aluminium Co. Ltd.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -6621,17 +6654,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nippon Life India Asset Management Ltd.</t>
+          <t>NHPC Ltd.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -6641,17 +6674,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NLC India Ltd.</t>
+          <t>Nippon Life India Asset Management Ltd.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6661,17 +6694,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NMDC Ltd.</t>
+          <t>NLC India Ltd.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -6681,17 +6714,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NTPC Green Energy Ltd.</t>
+          <t>NMDC Ltd.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NTPCGREEN</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -6701,17 +6734,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Oberoi Realty Ltd.</t>
+          <t>NTPC Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>NTPCGREEN</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -6721,17 +6754,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Oil India Ltd.</t>
+          <t>Oberoi Realty Ltd.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -6741,17 +6774,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>One 97 Communications Ltd.</t>
+          <t>Oil India Ltd.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6794,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ONE WAM Ltd.</t>
+          <t>One 97 Communications Ltd.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6781,17 +6814,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Oracle Financial Services Software Ltd.</t>
+          <t>ONE WAM Ltd.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6801,17 +6834,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Page Industries Ltd.</t>
+          <t>Oracle Financial Services Software Ltd.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -6821,17 +6854,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Patanjali Foods Ltd.</t>
+          <t>Page Industries Ltd.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -6841,17 +6874,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PB Fintech Ltd.</t>
+          <t>Patanjali Foods Ltd.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -6861,17 +6894,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Persistent Systems Ltd.</t>
+          <t>PB Fintech Ltd.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6881,17 +6914,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Petronet LNG Ltd.</t>
+          <t>Persistent Systems Ltd.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -6901,17 +6934,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Phoenix Mills Ltd.</t>
+          <t>Petronet LNG Ltd.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -6921,17 +6954,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PI Industries Ltd.</t>
+          <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -6941,17 +6974,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Polycab India Ltd.</t>
+          <t>PI Industries Ltd.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>PIIND</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -6961,17 +6994,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Premier Energies Ltd.</t>
+          <t>Piramal Finance Ltd.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PREMIERENE</t>
+          <t>PIRAMALFIN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6981,17 +7014,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Prestige Estates Projects Ltd.</t>
+          <t>Premier Energies Ltd.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>PREMIERENE</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7001,17 +7034,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Radico Khaitan Ltd</t>
+          <t>Prestige Estates Projects Ltd.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -7021,17 +7054,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Rail Vikas Nigam Ltd.</t>
+          <t>Radico Khaitan Ltd</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -7041,17 +7074,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SBI Cards and Payment Services Ltd.</t>
+          <t>Rail Vikas Nigam Ltd.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>RVNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -7061,17 +7094,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Schaeffler India Ltd.</t>
+          <t>REC Ltd.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7081,17 +7114,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SJVN Ltd.</t>
+          <t>SBI Cards and Payment Services Ltd.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7101,17 +7134,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SRF Ltd.</t>
+          <t>Schaeffler India Ltd.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -7121,17 +7154,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Steel Authority of India Ltd.</t>
+          <t>Shree Cement Ltd.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -7141,17 +7174,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Sundaram Finance Ltd.</t>
+          <t>SRF Ltd.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SUNDARMFIN</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -7161,17 +7194,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Supreme Industries Ltd.</t>
+          <t>Steel Authority of India Ltd.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -7181,17 +7214,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Suzlon Energy Ltd.</t>
+          <t>Sundaram Finance Ltd.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>SUNDARMFIN</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7201,17 +7234,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Swiggy Ltd.</t>
+          <t>Supreme Industries Ltd.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7221,17 +7254,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Tata Communications Ltd.</t>
+          <t>Suzlon Energy Ltd.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7241,17 +7274,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Tata Elxsi Ltd.</t>
+          <t>Swiggy Ltd.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -7261,17 +7294,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tata Investment Corporation Ltd.</t>
+          <t>Tata Communications Ltd.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>TATAINVEST</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -7281,12 +7314,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>The New India Assurance Company Ltd.</t>
+          <t>Tata Investment Corporation Ltd.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>NIACL</t>
+          <t>TATAINVEST</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7381,17 +7414,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>UNO Minda Ltd.</t>
+          <t>United Spirits Ltd.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -7401,17 +7434,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>UPL Ltd.</t>
+          <t>UNO Minda Ltd.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -7421,17 +7454,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Vishal Mega Mart Ltd.</t>
+          <t>UPL Ltd.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -7441,17 +7474,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Vodafone Idea Ltd.</t>
+          <t>Vishal Mega Mart Ltd.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>VMM</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -568,10 +568,10 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21853.3</v>
+        <v>21867.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.33</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3560606060606061</v>
+        <v>0.4029850746268657</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>799.6084888401025</v>
+        <v>769.9823943661972</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2370726953891595</v>
+        <v>0.201890888267142</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03658982802780827</v>
+        <v>0.0352112676056338</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>64.39393939393939</v>
+        <v>59.70149253731343</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>97.4145390778319</v>
+        <v>90.37817765342839</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.30011929910714</v>
+        <v>68.90449807214792</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.95422682863472</v>
+        <v>28.3128226215368</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23152.04555997816</v>
+        <v>21800.37495339634</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05943018033789693</v>
+        <v>-0.003069626002225156</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>36.97113475580579</v>
+        <v>35.16938435357687</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29562.43319279366</v>
+        <v>27079.80677295219</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3527674627078594</v>
+        <v>0.2383586039991856</v>
       </c>
     </row>
     <row r="16">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="30" t="n">
         <v>0.2653102993441867</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.1793215921783975</v>
+        <v>0.1653034601227512</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0.2087496993406504</v>
@@ -860,20 +860,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.02964426021457878</v>
+        <v>0.03939406902517728</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>0.2211416042343128</v>
+        <v>0.1357141323258862</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0.1736020897012249</v>
       </c>
-      <c r="F20" s="30" t="n"/>
+      <c r="F20" s="30" t="n">
+        <v>0.156637734321603</v>
+      </c>
       <c r="G20" s="30" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="21">
@@ -883,20 +885,20 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>-0.01141617236566639</v>
+        <v>0.00241284256585611</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>0.1661927584662644</v>
+        <v>0.1976536954943249</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>0.158578639409193</v>
+        <v>0.1509158844472421</v>
       </c>
       <c r="F21" s="30" t="n"/>
       <c r="G21" s="30" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="22">
@@ -936,7 +938,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -946,7 +948,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
@@ -969,7 +971,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2288,6 +2290,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>21867.5</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2404,7 +2425,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$42,D2,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$42,D2,$C$2:$C$42,C2)+1)/2)/COUNTIFS($D$2:$D$42,D2,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$43,D2,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$43,D2,$C$2:$C$43,C2)+1)/2)/COUNTIFS($D$2:$D$43,D2,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2449,7 +2470,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$42,D3,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$42,D3,$C$2:$C$42,C3)+1)/2)/COUNTIFS($D$2:$D$42,D3,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$43,D3,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$43,D3,$C$2:$C$43,C3)+1)/2)/COUNTIFS($D$2:$D$43,D3,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2468,7 +2489,10 @@
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="30" t="n"/>
+      <c r="L3" s="30">
+        <f>IFERROR((B43/B3)^(1/10)-1,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="n">
@@ -2491,7 +2515,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$42,D4,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$42,D4,$C$2:$C$42,C4)+1)/2)/COUNTIFS($D$2:$D$42,D4,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$43,D4,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$43,D4,$C$2:$C$43,C4)+1)/2)/COUNTIFS($D$2:$D$43,D4,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2533,7 +2557,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$42,D5,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$42,D5,$C$2:$C$42,C5)+1)/2)/COUNTIFS($D$2:$D$42,D5,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$43,D5,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$43,D5,$C$2:$C$43,C5)+1)/2)/COUNTIFS($D$2:$D$43,D5,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2578,7 +2602,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$42,D6,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$42,D6,$C$2:$C$42,C6)+1)/2)/COUNTIFS($D$2:$D$42,D6,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$43,D6,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$43,D6,$C$2:$C$43,C6)+1)/2)/COUNTIFS($D$2:$D$43,D6,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2623,7 +2647,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$42,D7,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$42,D7,$C$2:$C$42,C7)+1)/2)/COUNTIFS($D$2:$D$42,D7,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$43,D7,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$43,D7,$C$2:$C$43,C7)+1)/2)/COUNTIFS($D$2:$D$43,D7,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2668,7 +2692,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$42,D8,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$42,D8,$C$2:$C$42,C8)+1)/2)/COUNTIFS($D$2:$D$42,D8,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$43,D8,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$43,D8,$C$2:$C$43,C8)+1)/2)/COUNTIFS($D$2:$D$43,D8,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2713,7 +2737,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$42,D9,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$42,D9,$C$2:$C$42,C9)+1)/2)/COUNTIFS($D$2:$D$42,D9,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$43,D9,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$43,D9,$C$2:$C$43,C9)+1)/2)/COUNTIFS($D$2:$D$43,D9,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2758,7 +2782,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$42,D10,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$42,D10,$C$2:$C$42,C10)+1)/2)/COUNTIFS($D$2:$D$42,D10,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$43,D10,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$43,D10,$C$2:$C$43,C10)+1)/2)/COUNTIFS($D$2:$D$43,D10,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2803,7 +2827,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$42,D11,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$42,D11,$C$2:$C$42,C11)+1)/2)/COUNTIFS($D$2:$D$42,D11,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$43,D11,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$43,D11,$C$2:$C$43,C11)+1)/2)/COUNTIFS($D$2:$D$43,D11,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2848,7 +2872,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$42,D12,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$42,D12,$C$2:$C$42,C12)+1)/2)/COUNTIFS($D$2:$D$42,D12,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$43,D12,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$43,D12,$C$2:$C$43,C12)+1)/2)/COUNTIFS($D$2:$D$43,D12,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2893,7 +2917,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$42,D13,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$42,D13,$C$2:$C$42,C13)+1)/2)/COUNTIFS($D$2:$D$42,D13,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$43,D13,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$43,D13,$C$2:$C$43,C13)+1)/2)/COUNTIFS($D$2:$D$43,D13,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2938,7 +2962,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$42,D14,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$42,D14,$C$2:$C$42,C14)+1)/2)/COUNTIFS($D$2:$D$42,D14,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$43,D14,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$43,D14,$C$2:$C$43,C14)+1)/2)/COUNTIFS($D$2:$D$43,D14,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2983,7 +3007,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$42,D15,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$42,D15,$C$2:$C$42,C15)+1)/2)/COUNTIFS($D$2:$D$42,D15,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$43,D15,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$43,D15,$C$2:$C$43,C15)+1)/2)/COUNTIFS($D$2:$D$43,D15,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3028,7 +3052,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$42,D16,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$42,D16,$C$2:$C$42,C16)+1)/2)/COUNTIFS($D$2:$D$42,D16,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$43,D16,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$43,D16,$C$2:$C$43,C16)+1)/2)/COUNTIFS($D$2:$D$43,D16,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3073,7 +3097,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$42,D17,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$42,D17,$C$2:$C$42,C17)+1)/2)/COUNTIFS($D$2:$D$42,D17,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$43,D17,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$43,D17,$C$2:$C$43,C17)+1)/2)/COUNTIFS($D$2:$D$43,D17,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3118,7 +3142,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$42,D18,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$42,D18,$C$2:$C$42,C18)+1)/2)/COUNTIFS($D$2:$D$42,D18,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$43,D18,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$43,D18,$C$2:$C$43,C18)+1)/2)/COUNTIFS($D$2:$D$43,D18,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3161,7 +3185,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$42,D19,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$42,D19,$C$2:$C$42,C19)+1)/2)/COUNTIFS($D$2:$D$42,D19,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$43,D19,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$43,D19,$C$2:$C$43,C19)+1)/2)/COUNTIFS($D$2:$D$43,D19,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3206,7 +3230,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$42,D20,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$42,D20,$C$2:$C$42,C20)+1)/2)/COUNTIFS($D$2:$D$42,D20,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$43,D20,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$43,D20,$C$2:$C$43,C20)+1)/2)/COUNTIFS($D$2:$D$43,D20,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3251,7 +3275,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$42,D21,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$42,D21,$C$2:$C$42,C21)+1)/2)/COUNTIFS($D$2:$D$42,D21,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$43,D21,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$43,D21,$C$2:$C$43,C21)+1)/2)/COUNTIFS($D$2:$D$43,D21,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3296,7 +3320,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$42,D22,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$42,D22,$C$2:$C$42,C22)+1)/2)/COUNTIFS($D$2:$D$42,D22,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$43,D22,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$43,D22,$C$2:$C$43,C22)+1)/2)/COUNTIFS($D$2:$D$43,D22,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3341,7 +3365,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$42,D23,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$42,D23,$C$2:$C$42,C23)+1)/2)/COUNTIFS($D$2:$D$42,D23,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$43,D23,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$43,D23,$C$2:$C$43,C23)+1)/2)/COUNTIFS($D$2:$D$43,D23,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3356,7 +3380,10 @@
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="30" t="n"/>
+      <c r="K23" s="30">
+        <f>IFERROR((B43/B23)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
@@ -3383,7 +3410,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$42,D24,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$42,D24,$C$2:$C$42,C24)+1)/2)/COUNTIFS($D$2:$D$42,D24,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$43,D24,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$43,D24,$C$2:$C$43,C24)+1)/2)/COUNTIFS($D$2:$D$43,D24,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3425,7 +3452,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$42,D25,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$42,D25,$C$2:$C$42,C25)+1)/2)/COUNTIFS($D$2:$D$42,D25,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$43,D25,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$43,D25,$C$2:$C$43,C25)+1)/2)/COUNTIFS($D$2:$D$43,D25,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3467,7 +3494,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$42,D26,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$42,D26,$C$2:$C$42,C26)+1)/2)/COUNTIFS($D$2:$D$42,D26,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$43,D26,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$43,D26,$C$2:$C$43,C26)+1)/2)/COUNTIFS($D$2:$D$43,D26,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3509,7 +3536,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$42,D27,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$42,D27,$C$2:$C$42,C27)+1)/2)/COUNTIFS($D$2:$D$42,D27,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$43,D27,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$43,D27,$C$2:$C$43,C27)+1)/2)/COUNTIFS($D$2:$D$43,D27,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3551,7 +3578,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$42,D28,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$42,D28,$C$2:$C$42,C28)+1)/2)/COUNTIFS($D$2:$D$42,D28,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$43,D28,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$43,D28,$C$2:$C$43,C28)+1)/2)/COUNTIFS($D$2:$D$43,D28,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3593,7 +3620,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$42,D29,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$42,D29,$C$2:$C$42,C29)+1)/2)/COUNTIFS($D$2:$D$42,D29,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$43,D29,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$43,D29,$C$2:$C$43,C29)+1)/2)/COUNTIFS($D$2:$D$43,D29,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3635,7 +3662,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$42,D30,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$42,D30,$C$2:$C$42,C30)+1)/2)/COUNTIFS($D$2:$D$42,D30,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$43,D30,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$43,D30,$C$2:$C$43,C30)+1)/2)/COUNTIFS($D$2:$D$43,D30,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3677,7 +3704,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$42,D31,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$42,D31,$C$2:$C$42,C31)+1)/2)/COUNTIFS($D$2:$D$42,D31,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$43,D31,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$43,D31,$C$2:$C$43,C31)+1)/2)/COUNTIFS($D$2:$D$43,D31,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3688,7 +3715,10 @@
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="30" t="n"/>
+      <c r="J31" s="30">
+        <f>IFERROR((B43/B31)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K31" s="30" t="n"/>
       <c r="L31" s="30" t="n"/>
     </row>
@@ -3716,7 +3746,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$42,D32,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$42,D32,$C$2:$C$42,C32)+1)/2)/COUNTIFS($D$2:$D$42,D32,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$43,D32,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$43,D32,$C$2:$C$43,C32)+1)/2)/COUNTIFS($D$2:$D$43,D32,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3755,7 +3785,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$42,D33,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$42,D33,$C$2:$C$42,C33)+1)/2)/COUNTIFS($D$2:$D$42,D33,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$43,D33,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$43,D33,$C$2:$C$43,C33)+1)/2)/COUNTIFS($D$2:$D$43,D33,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3794,7 +3824,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$42,D34,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$42,D34,$C$2:$C$42,C34)+1)/2)/COUNTIFS($D$2:$D$42,D34,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$43,D34,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$43,D34,$C$2:$C$43,C34)+1)/2)/COUNTIFS($D$2:$D$43,D34,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3833,7 +3863,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$42,D35,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$42,D35,$C$2:$C$42,C35)+1)/2)/COUNTIFS($D$2:$D$42,D35,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$43,D35,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$43,D35,$C$2:$C$43,C35)+1)/2)/COUNTIFS($D$2:$D$43,D35,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3872,7 +3902,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$42,D36,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$42,D36,$C$2:$C$42,C36)+1)/2)/COUNTIFS($D$2:$D$42,D36,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$43,D36,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$43,D36,$C$2:$C$43,C36)+1)/2)/COUNTIFS($D$2:$D$43,D36,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3911,7 +3941,7 @@
         <v/>
       </c>
       <c r="G37" s="30">
-        <f>IF(C37="","",(COUNTIFS($D$2:$D$42,D37,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$42,D37,$C$2:$C$42,C37)+1)/2)/COUNTIFS($D$2:$D$42,D37,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$43,D37,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$43,D37,$C$2:$C$43,C37)+1)/2)/COUNTIFS($D$2:$D$43,D37,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H37">
@@ -3950,7 +3980,7 @@
         <v/>
       </c>
       <c r="G38" s="30">
-        <f>IF(C38="","",(COUNTIFS($D$2:$D$42,D38,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$42,D38,$C$2:$C$42,C38)+1)/2)/COUNTIFS($D$2:$D$42,D38,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C38="","",(COUNTIFS($D$2:$D$43,D38,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$43,D38,$C$2:$C$43,C38)+1)/2)/COUNTIFS($D$2:$D$43,D38,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H38">
@@ -3989,14 +4019,17 @@
         <v/>
       </c>
       <c r="G39" s="30">
-        <f>IF(C39="","",(COUNTIFS($D$2:$D$42,D39,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$42,D39,$C$2:$C$42,C39)+1)/2)/COUNTIFS($D$2:$D$42,D39,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C39="","",(COUNTIFS($D$2:$D$43,D39,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$43,D39,$C$2:$C$43,C39)+1)/2)/COUNTIFS($D$2:$D$43,D39,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H39">
         <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I39" s="30" t="n"/>
+      <c r="I39" s="30">
+        <f>IFERROR(B43/B39-1,"")</f>
+        <v/>
+      </c>
       <c r="J39" s="30" t="n"/>
       <c r="K39" s="30" t="n"/>
       <c r="L39" s="30" t="n"/>
@@ -4025,7 +4058,7 @@
         <v/>
       </c>
       <c r="G40" s="30">
-        <f>IF(C40="","",(COUNTIFS($D$2:$D$42,D40,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$42,D40,$C$2:$C$42,C40)+1)/2)/COUNTIFS($D$2:$D$42,D40,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C40="","",(COUNTIFS($D$2:$D$43,D40,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$43,D40,$C$2:$C$43,C40)+1)/2)/COUNTIFS($D$2:$D$43,D40,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H40">
@@ -4061,7 +4094,7 @@
         <v/>
       </c>
       <c r="G41" s="30">
-        <f>IF(C41="","",(COUNTIFS($D$2:$D$42,D41,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$42,D41,$C$2:$C$42,C41)+1)/2)/COUNTIFS($D$2:$D$42,D41,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C41="","",(COUNTIFS($D$2:$D$43,D41,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$43,D41,$C$2:$C$43,C41)+1)/2)/COUNTIFS($D$2:$D$43,D41,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H41">
@@ -4097,7 +4130,7 @@
         <v/>
       </c>
       <c r="G42" s="30">
-        <f>IF(C42="","",(COUNTIFS($D$2:$D$42,D42,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$42,D42,$C$2:$C$42,C42)+1)/2)/COUNTIFS($D$2:$D$42,D42,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C42="","",(COUNTIFS($D$2:$D$43,D42,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$43,D42,$C$2:$C$43,C42)+1)/2)/COUNTIFS($D$2:$D$43,D42,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H42">
@@ -4108,6 +4141,42 @@
       <c r="J42" s="30" t="n"/>
       <c r="K42" s="30" t="n"/>
       <c r="L42" s="30" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B43" s="24" t="n">
+        <v>21867.5</v>
+      </c>
+      <c r="C43" s="25" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E43" s="33">
+        <f>IFERROR(B43/C43,"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="30">
+        <f>IF(AND(D43=D39,E39&lt;&gt;""),E43/E39-1,"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="30">
+        <f>IF(C43="","",(COUNTIFS($D$2:$D$43,D43,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$43,D43,$C$2:$C$43,C43)+1)/2)/COUNTIFS($D$2:$D$43,D43,$C$2:$C$43,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H43">
+        <f>IF(G43="","",IF(G43&lt;=20%,"Q1 Cheapest",IF(G43&lt;=40%,"Q2",IF(G43&lt;=60%,"Q3",IF(G43&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I43" s="30" t="n"/>
+      <c r="J43" s="30" t="n"/>
+      <c r="K43" s="30" t="n"/>
+      <c r="L43" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4122,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4130,7 +4199,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4444,6 +4513,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>21867.5</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.402985074627</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.201890888267</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4484,7 +4586,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21867.5</v>
+        <v>21643.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.4029850746268657</v>
+        <v>0.3805970149253731</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>769.9823943661972</v>
+        <v>770.2437722419928</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.201890888267142</v>
+        <v>0.2021645976713404</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0352112676056338</v>
+        <v>0.03558718861209964</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>59.70149253731343</v>
+        <v>61.94029850746269</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>90.37817765342839</v>
+        <v>90.43291953426808</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>68.90449807214792</v>
+        <v>70.48808481550431</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.3128226215368</v>
+        <v>28.1579597239693</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>21800.37495339634</v>
+        <v>21688.49311642822</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.003069626002225156</v>
+        <v>0.00206262362880083</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.16938435357687</v>
+        <v>35.17975872202287</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27079.80677295219</v>
+        <v>27096.99006461404</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2383586039991856</v>
+        <v>0.2519487089687853</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4546,6 +4546,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>21643.85</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.380597014925</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.202164597671</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4586,7 +4619,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21643.85</v>
+        <v>21755.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.1</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3805970149253731</v>
+        <v>0.3955223880597015</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>770.2437722419928</v>
+        <v>770.0991150442478</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2021645976713404</v>
+        <v>0.2019135452530048</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03558718861209964</v>
+        <v>0.03539823008849557</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>61.94029850746269</v>
+        <v>60.44776119402986</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>90.43291953426808</v>
+        <v>90.38270905060095</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.48808481550431</v>
+        <v>69.42824555100118</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.1579597239693</v>
+        <v>28.22826974228707</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>21688.49311642822</v>
+        <v>21738.56554776559</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.00206262362880083</v>
+        <v>-0.0007692126624045947</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.17975872202287</v>
+        <v>35.17024311807532</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27096.99006461404</v>
+        <v>27084.57310112085</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2519487089687853</v>
+        <v>0.2449643581619583</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4579,6 +4579,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>21755.3</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.39552238806</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.201913545253</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4619,7 +4652,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21755.3</v>
+        <v>21979.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.25</v>
+        <v>28.54</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3955223880597015</v>
+        <v>0.4104477611940299</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>770.0991150442478</v>
+        <v>770.1278906797478</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2019135452530048</v>
+        <v>0.2021271465876009</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03539823008849557</v>
+        <v>0.0350385423966363</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>60.44776119402986</v>
+        <v>58.95522388059702</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>90.38270905060095</v>
+        <v>90.42542931752018</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>69.42824555100118</v>
+        <v>68.39628551167397</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.22826974228707</v>
+        <v>28.31549571567685</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>21738.56554776559</v>
+        <v>21806.55298906565</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.0007692126624045947</v>
+        <v>-0.007866302884482979</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.17024311807532</v>
+        <v>35.17833921894604</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27084.57310112085</v>
+        <v>27091.82018030356</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2449643581619583</v>
+        <v>0.2325977301662945</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4612,6 +4612,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>21979.45</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.410447761194</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.202127146588</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4652,7 +4685,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21979.45</v>
+        <v>21838</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.54</v>
+        <v>28.36</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.4104477611940299</v>
+        <v>0.3955223880597015</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>770.1278906797478</v>
+        <v>770.0282087447109</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2021271465876009</v>
+        <v>0.2018844887113034</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0350385423966363</v>
+        <v>0.03526093088857546</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>58.95522388059702</v>
+        <v>60.44776119402986</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>90.42542931752018</v>
+        <v>90.37689774226068</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>68.39628551167397</v>
+        <v>69.4265021584991</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.31549571567685</v>
+        <v>28.29020017210688</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>21806.55298906565</v>
+        <v>21784.25216355678</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.007866302884482979</v>
+        <v>-0.002461206907373614</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.17833921894604</v>
+        <v>35.16914179212615</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27091.82018030356</v>
+        <v>27081.23125727965</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2325977301662945</v>
+        <v>0.240096678142671</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4645,6 +4645,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>21838</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.39552238806</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.201884488711</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4685,7 +4718,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21838</v>
+        <v>21311.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.36</v>
+        <v>27.67</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3955223880597015</v>
+        <v>0.3805970149253731</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>770.0282087447109</v>
+        <v>770.2023852547885</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2018844887113034</v>
+        <v>0.2020376319669108</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03526093088857546</v>
+        <v>0.03614022406938923</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>60.44776119402986</v>
+        <v>61.94029850746269</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>90.37689774226068</v>
+        <v>90.40752639338217</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>69.4265021584991</v>
+        <v>70.48046687323853</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.29020017210688</v>
+        <v>27.97337974245932</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>21784.25216355678</v>
+        <v>21545.16380128015</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.002461206907373614</v>
+        <v>0.01096421187059349</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.16914179212615</v>
+        <v>35.17494635906583</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27081.23125727965</v>
+        <v>27091.82758696174</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.240096678142671</v>
+        <v>0.2712304430453858</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4678,6 +4678,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>21311.5</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.380597014925</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.202037631967</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4718,7 +4751,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21311.5</v>
+        <v>21603.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.67</v>
+        <v>28.05</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>770.2023852547885</v>
+        <v>770.1693404634581</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2020376319669108</v>
+        <v>0.2020615032238271</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03614022406938923</v>
+        <v>0.035650623885918</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>90.40752639338217</v>
+        <v>90.41230064476542</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.48046687323853</v>
+        <v>70.48189914865351</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.97337974245932</v>
+        <v>28.1360647559279</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>21545.16380128015</v>
+        <v>21669.53443631014</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01096421187059349</v>
+        <v>0.003068262243419051</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.17494635906583</v>
+        <v>35.17585114790654</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27091.82758696174</v>
+        <v>27091.36207882396</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2712304430453858</v>
+        <v>0.2540410391410532</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4711,6 +4711,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>21603.25</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.380597014925</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.202061503224</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4751,7 +4784,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21603.25</v>
+        <v>21620.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.05</v>
+        <v>28.07</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>770.1693404634581</v>
+        <v>770.2351264695404</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2020615032238271</v>
+        <v>0.2022553488384677</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.035650623885918</v>
+        <v>0.03562522265764161</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>90.41230064476542</v>
+        <v>90.45106976769355</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.48189914865351</v>
+        <v>70.49352988553194</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.1360647559279</v>
+        <v>28.14601505117205</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>21669.53443631014</v>
+        <v>21679.04946255309</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.003068262243419051</v>
+        <v>0.002708053123336107</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.17585114790654</v>
+        <v>35.18319845054604</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27091.36207882396</v>
+        <v>27099.33530815927</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2540410391410532</v>
+        <v>0.2534092786086941</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4744,6 +4744,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>21620.5</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.380597014925</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.202255348838</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4784,7 +4817,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21620.5</v>
+        <v>21829.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.07</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3805970149253731</v>
+        <v>0.3955223880597015</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>770.2351264695404</v>
+        <v>770.2681721947778</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2022553488384677</v>
+        <v>0.20286052526169</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03562522265764161</v>
+        <v>0.03528581510232887</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>61.94029850746269</v>
+        <v>60.44776119402986</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>90.45106976769355</v>
+        <v>90.57210505233799</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.49352988553194</v>
+        <v>69.4850643515223</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.14601505117205</v>
+        <v>28.28665536007258</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>21679.04946255309</v>
+        <v>21788.31032170672</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.002708053123336107</v>
+        <v>-0.001882309101179147</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.18319845054604</v>
+        <v>35.20613636606166</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27099.33530815927</v>
+        <v>27118.16630872641</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2534092786086941</v>
+        <v>0.242277218280228</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4777,6 +4777,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>21829.4</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.39552238806</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.202860525262</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4817,7 +4850,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21829.4</v>
+        <v>21820.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.34</v>
+        <v>28.33</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>770.2681721947778</v>
+        <v>770.222379103424</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.20286052526169</v>
+        <v>0.202628206833571</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03528581510232887</v>
+        <v>0.03529827038475115</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>90.57210505233799</v>
+        <v>90.5256413667142</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>69.4850643515223</v>
+        <v>69.47112524583515</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.28665536007258</v>
+        <v>28.27875715539889</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>21788.31032170672</v>
+        <v>21780.93161431931</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.001882309101179147</v>
+        <v>-0.001808783784013834</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.20613636606166</v>
+        <v>35.19733083386901</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27118.16630872641</v>
+        <v>27109.77189295289</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.242277218280228</v>
+        <v>0.2424049005954469</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4810,6 +4810,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>21820.4</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.39552238806</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.202628206834</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4850,7 +4883,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21820.4</v>
+        <v>21756.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.33</v>
+        <v>28.18</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3955223880597015</v>
+        <v>0.3805970149253731</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>770.222379103424</v>
+        <v>772.0493257629524</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.202628206833571</v>
+        <v>0.2067864349204591</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03529827038475115</v>
+        <v>0.035486160397445</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>60.44776119402986</v>
+        <v>61.94029850746269</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>90.5256413667142</v>
+        <v>91.35728698409183</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>69.47112524583515</v>
+        <v>70.76539505045143</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.27875715539889</v>
+        <v>28.19682122351001</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>21780.93161431931</v>
+        <v>21769.33681426941</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.001808783784013834</v>
+        <v>0.0005969206355573853</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.19733083386901</v>
+        <v>35.2978906014672</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27109.77189295289</v>
+        <v>27251.71263971721</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2424049005954469</v>
+        <v>0.2525866075751315</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4843,6 +4843,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>21756.35</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.380597014925</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.20678643492</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4883,7 +4916,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21756.35</v>
+        <v>21736.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.18</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>772.0493257629524</v>
+        <v>772.9996443812233</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2067864349204591</v>
+        <v>0.2074534760800537</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.035486160397445</v>
+        <v>0.03556187766714082</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>91.35728698409183</v>
+        <v>91.49069521601075</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.76539505045143</v>
+        <v>70.80541752002711</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.19682122351001</v>
+        <v>28.19030373174515</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>21769.33681426941</v>
+        <v>21791.09475963768</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.0005969206355573853</v>
+        <v>0.002500132707864644</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.2978906014672</v>
+        <v>35.30619240515633</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27251.71263971721</v>
+        <v>27291.67417364089</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2525866075751315</v>
+        <v>0.255554495204706</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4876,6 +4876,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>21736.75</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.380597014925</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.20745347608</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4916,7 +4949,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21736.75</v>
+        <v>21499.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.12</v>
+        <v>27.71</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>772.9996443812233</v>
+        <v>775.8679177192349</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2074534760800537</v>
+        <v>0.2106685331213984</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03556187766714082</v>
+        <v>0.03608805485384338</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>91.49069521601075</v>
+        <v>92.13370662427968</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.80541752002711</v>
+        <v>70.99832094250779</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.19030373174515</v>
+        <v>28.21213540331639</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>21791.09475963768</v>
+        <v>21888.8907497842</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.002500132707864644</v>
+        <v>0.0181210899789388</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.30619240515633</v>
+        <v>35.34620608650518</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27291.67417364089</v>
+        <v>27423.98731561172</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.255554495204706</v>
+        <v>0.2755758241250517</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4909,6 +4909,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>21499.3</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.380597014925</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.210668533121</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4949,7 +4982,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21499.3</v>
+        <v>21200.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.71</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3805970149253731</v>
+        <v>0.3507462686567164</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>775.8679177192349</v>
+        <v>775.9974377745242</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2106685331213984</v>
+        <v>0.2184530621048599</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03608805485384338</v>
+        <v>0.03660322108345535</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>61.94029850746269</v>
+        <v>64.92537313432835</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>92.13370662427968</v>
+        <v>93.69061242097199</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.99832094250779</v>
+        <v>73.55494492032145</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.21213540331639</v>
+        <v>28.30021178838641</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>21888.8907497842</v>
+        <v>21960.89183626424</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.0181210899789388</v>
+        <v>0.03587890879891709</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.34620608650518</v>
+        <v>35.4430901100822</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27423.98731561172</v>
+        <v>27503.74711223537</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2755758241250517</v>
+        <v>0.2973312631801686</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4942,6 +4942,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>21200.25</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.350746268657</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.218453062105</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4982,7 +5015,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21200.25</v>
+        <v>21028.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.32</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3507462686567164</v>
+        <v>0.3208955223880597</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>775.9974377745242</v>
+        <v>777.9744728079911</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2184530621048599</v>
+        <v>0.2215573563630018</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03660322108345535</v>
+        <v>0.03699593044765076</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>64.92537313432835</v>
+        <v>67.91044776119404</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>93.69061242097199</v>
+        <v>94.31147127260036</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>73.55494492032145</v>
+        <v>75.83075481461593</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.30021178838641</v>
+        <v>28.33533466056425</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>21960.89183626424</v>
+        <v>22044.16704439047</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03587890879891709</v>
+        <v>0.04829207031314242</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.4430901100822</v>
+        <v>35.48172526947781</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27503.74711223537</v>
+        <v>27603.87651083998</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2973312631801686</v>
+        <v>0.3126794402322535</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4975,6 +4975,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>21028.65</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.320895522388</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.221557356363</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5015,7 +5048,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21028.65</v>
+        <v>20592.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.03</v>
+        <v>26.42</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3208955223880597</v>
+        <v>0.2462686567164179</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>777.9744728079911</v>
+        <v>779.4379258137774</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2215573563630018</v>
+        <v>0.2238639631306507</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03699593044765076</v>
+        <v>0.03785011355034065</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>67.91044776119404</v>
+        <v>75.37313432835822</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>94.31147127260036</v>
+        <v>94.77279262613014</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>75.83075481461593</v>
+        <v>81.19303181768979</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.33533466056425</v>
+        <v>28.36143226856393</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22044.16704439047</v>
+        <v>22105.9759405174</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04829207031314242</v>
+        <v>0.07348343181544004</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.48172526947781</v>
+        <v>35.62838468651558</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27603.87651083998</v>
+        <v>27770.11426015305</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3126794402322535</v>
+        <v>0.3485384059998327</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5008,6 +5008,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>20592.75</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.246268656716</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.223863963131</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5048,7 +5081,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>20592.75</v>
+        <v>20812.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.42</v>
+        <v>26.69</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.2462686567164179</v>
+        <v>0.2761194029850746</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>779.4379258137774</v>
+        <v>779.7770700636943</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2238639631306507</v>
+        <v>0.2250082655117169</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03785011355034065</v>
+        <v>0.03746721618583739</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>75.37313432835822</v>
+        <v>72.38805970149254</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>94.77279262613014</v>
+        <v>95.00165310234338</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>81.19303181768979</v>
+        <v>79.17213772174779</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.36143226856393</v>
+        <v>28.37437923264685</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22105.9759405174</v>
+        <v>22125.6903029095</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07348343181544004</v>
+        <v>0.06310900084851467</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.62838468651558</v>
+        <v>35.72483956893335</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27770.11426015305</v>
+        <v>27857.41072755838</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3485384059998327</v>
+        <v>0.3385102873335839</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5041,6 +5041,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>20812.25</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.276119402985</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.225008265512</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5081,7 +5114,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>20812.25</v>
+        <v>21003.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.69</v>
+        <v>26.47</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.2761194029850746</v>
+        <v>0.2462686567164179</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>779.7770700636943</v>
+        <v>793.4699659992446</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2250082655117169</v>
+        <v>0.245334275529131</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03746721618583739</v>
+        <v>0.03777861730260672</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>72.38805970149254</v>
+        <v>75.37313432835822</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>95.00165310234338</v>
+        <v>99.06685510582621</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>79.17213772174779</v>
+        <v>82.48125056159861</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.37437923264685</v>
+        <v>28.92544189676914</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22125.6903029095</v>
+        <v>22951.46939834253</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06310900084851467</v>
+        <v>0.09276319972682812</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35.72483956893335</v>
+        <v>37.5273177335677</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>27857.41072755838</v>
+        <v>29776.79952609681</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3385102873335839</v>
+        <v>0.417730175049781</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5074,6 +5074,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>21003.15</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.246268656716</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.245334275529</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5114,7 +5147,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -6404,12 +6437,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ICICI Lombard General Insurance Company Ltd.</t>
+          <t>ICICI Life Insurance Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>ICICILIFE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6424,12 +6457,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ICICI Prudential Asset Management Company Ltd.</t>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ICICIAMC</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6444,12 +6477,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ICICI Prudential Life Insurance Company Ltd.</t>
+          <t>ICICI Prudential Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>ICICIAMC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21003.15</v>
+        <v>21064.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.47</v>
+        <v>26.55</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.2462686567164179</v>
+        <v>0.2761194029850746</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>793.4699659992446</v>
+        <v>793.4011299435027</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.245334275529131</v>
+        <v>0.2442405428112766</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03777861730260672</v>
+        <v>0.03766478342749529</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>75.37313432835822</v>
+        <v>72.38805970149254</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>99.06685510582621</v>
+        <v>98.84810856225532</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>82.48125056159861</v>
+        <v>80.32607435972136</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.92544189676914</v>
+        <v>28.89914465367115</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22951.46939834253</v>
+        <v>22928.61402262343</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.09276319972682812</v>
+        <v>0.08848002462038229</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>37.5273177335677</v>
+        <v>37.41718197383037</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29776.79952609681</v>
+        <v>29686.83445733867</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.417730175049781</v>
+        <v>0.4093100555115015</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5107,6 +5107,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>21064.8</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.276119402985</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.244240542811</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5147,7 +5180,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21064.8</v>
+        <v>21245.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.55</v>
+        <v>26.79</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.2761194029850746</v>
+        <v>0.291044776119403</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>793.4011299435027</v>
+        <v>793.0309817095931</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2442405428112766</v>
+        <v>0.2447339669203095</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03766478342749529</v>
+        <v>0.03732736095558045</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>72.38805970149254</v>
+        <v>70.89552238805969</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>98.84810856225532</v>
+        <v>98.94679338406189</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>80.32607435972136</v>
+        <v>79.31090368686034</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.89914465367115</v>
+        <v>28.91365978117573</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22928.61402262343</v>
+        <v>22929.42800108297</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.08848002462038229</v>
+        <v>0.07927061519879541</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>37.41718197383037</v>
+        <v>37.46686837182682</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29686.83445733867</v>
+        <v>29712.38740649393</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4093100555115015</v>
+        <v>0.3985393195904001</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5140,6 +5140,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>21245.3</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>26.79</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.291044776119</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.24473396692</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5180,7 +5213,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-150.xlsx
+++ b/docs/downloads/indices/nifty-midcap-150.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21245.3</v>
+        <v>21047.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.79</v>
+        <v>26.27</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.291044776119403</v>
+        <v>0.2313432835820896</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>793.0309817095931</v>
+        <v>801.1990864103541</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2447339669203095</v>
+        <v>0.2574310007464873</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03732736095558045</v>
+        <v>0.03806623524933384</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>70.89552238805969</v>
+        <v>76.86567164179104</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>98.94679338406189</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>79.31090368686034</v>
+        <v>83.80597014925372</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.91365978117573</v>
+        <v>28.99142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22929.42800108297</v>
+        <v>23227.90608515961</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07927061519879541</v>
+        <v>0.1035945402142586</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>37.46686837182682</v>
+        <v>37.99714285714285</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29712.38740649393</v>
+        <v>30443.27614334656</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3985393195904001</v>
+        <v>0.4464081788025447</v>
       </c>
     </row>
     <row r="16">
@@ -4191,7 +4191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5173,6 +5173,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>21047.5</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.231343283582</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.257431000746</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5213,7 +5246,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
